--- a/education_surveys/016_child_flexible_thinking_survey--education_surveys.xlsx
+++ b/education_surveys/016_child_flexible_thinking_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'adapts_easily_and_stays_calm',_'value':_'easy'}</t>
+          <t>adapts_easily_and_stays_calm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Adapts easily and stays calm', 'value': 'easy'}</t>
+          <t>Adapts easily and stays calm</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_struggles_but_recovers',_'value':_'moderate'}</t>
+          <t>somewhat_struggles_but_recovers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat struggles but recovers', 'value': 'moderate'}</t>
+          <t>Somewhat struggles but recovers</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'struggles_significantly_or_melts_down',_'value':_'difficult'}</t>
+          <t>struggles_significantly_or_melts_down</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Struggles significantly or melts down', 'value': 'difficult'}</t>
+          <t>Struggles significantly or melts down</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'willing_to_try_new_things',_'value':_'willing'}</t>
+          <t>willing_to_try_new_things</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Willing to try new things', 'value': 'willing'}</t>
+          <t>Willing to try new things</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'needs_significant_encouragement',_'value':_'hesitant'}</t>
+          <t>needs_significant_encouragement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Needs significant encouragement', 'value': 'hesitant'}</t>
+          <t>Needs significant encouragement</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'refuses_to_try_new_foods',_'value':_'refused'}</t>
+          <t>refuses_to_try_new_foods</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Refuses to try new foods', 'value': 'refused'}</t>
+          <t>Refuses to try new foods</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'accepts_loss_calmly',_'value':_'calm'}</t>
+          <t>accepts_loss_calmly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Accepts loss calmly', 'value': 'calm'}</t>
+          <t>Accepts loss calmly</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'gets_frustrated_or_angry',_'value':_'frustrated'}</t>
+          <t>gets_frustrated_or_angry</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Gets frustrated or angry', 'value': 'frustrated'}</t>
+          <t>Gets frustrated or angry</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'refuses_to_continue_playing',_'value':_'quit'}</t>
+          <t>refuses_to_continue_playing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Refuses to continue playing', 'value': 'quit'}</t>
+          <t>Refuses to continue playing</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'tries_a_new_way_or_strategy',_'value':_'adaptive'}</t>
+          <t>tries_a_new_way_or_strategy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Tries a new way or strategy', 'value': 'adaptive'}</t>
+          <t>Tries a new way or strategy</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'asks_for_immediate_help',_'value':_'help'}</t>
+          <t>asks_for_immediate_help</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Asks for immediate help', 'value': 'help'}</t>
+          <t>Asks for immediate help</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'gives_up_quickly',_'value':_'gives_up'}</t>
+          <t>gives_up_quickly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Gives up quickly', 'value': 'gives_up'}</t>
+          <t>Gives up quickly</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'always_shares_willingly',_'value':_'always'}</t>
+          <t>always_shares_willingly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Always shares willingly', 'value': 'always'}</t>
+          <t>Always shares willingly</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'usually_shares_with_prompting',_'value':_'usually'}</t>
+          <t>usually_shares_with_prompting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Usually shares with prompting', 'value': 'usually'}</t>
+          <t>Usually shares with prompting</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_shares',_'value':_'rarely'}</t>
+          <t>rarely_shares</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely shares', 'value': 'rarely'}</t>
+          <t>Rarely shares</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_shows_patience',_'value':_true}</t>
+          <t>yes_-_shows_patience</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Shows patience', 'value': True}</t>
+          <t>Yes - Shows patience</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_struggles_with_waiting',_'value':_false}</t>
+          <t>no_-_struggles_with_waiting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'No - Struggles with waiting', 'value': False}</t>
+          <t>No - Struggles with waiting</t>
         </is>
       </c>
     </row>
